--- a/sample/sample.xlsx
+++ b/sample/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CHSA\claude_eunice\barnabas\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8CD37E1-05AE-40BA-B1E1-3A3AD7C6E41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C893E76-4BC6-4B66-AA91-7C9D8FD900B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B6CE4FE-6BBF-465D-9ECF-868AAEC2E883}"/>
   </bookViews>
@@ -527,6 +527,7 @@
     <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" customWidth="1"/>
     <col min="12" max="12" width="13.21875" customWidth="1"/>
+    <col min="13" max="13" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
